--- a/request_forms/023_watersports_equipment_hire_form--request_forms.xlsx
+++ b/request_forms/023_watersports_equipment_hire_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -753,7 +753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -825,7 +825,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jet_ski</t>
+          <t>jet ski</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>water_skate</t>
+          <t>water skate</t>
         </is>
       </c>
     </row>
@@ -944,24 +944,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>water_bike</t>
+          <t>water bike</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>watersports_equipment_hire_form_choices</t>
+          <t>equipment_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>water_skate</t>
+          <t>kayak</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>water_skate</t>
+          <t>kayak</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kayak</t>
+          <t>jet_ski</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kayak</t>
+          <t>jet ski</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>jet_ski</t>
+          <t>paddleboard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jet_ski</t>
+          <t>paddleboard</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>paddleboard</t>
+          <t>water_skate</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>paddleboard</t>
+          <t>water skate</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>water_skate</t>
+          <t>sail</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>water_skate</t>
+          <t>sail</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sail</t>
+          <t>wakeboard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sail</t>
+          <t>wakeboard</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wakeboard</t>
+          <t>parasail</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>wakeboard</t>
+          <t>parasail</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>parasail</t>
+          <t>windsurf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>parasail</t>
+          <t>windsurf</t>
         </is>
       </c>
     </row>
@@ -1092,29 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>windsurf</t>
+          <t>water_bike</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>windsurf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>equipment_type_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>water_bike</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>water_bike</t>
+          <t>water bike</t>
         </is>
       </c>
     </row>
